--- a/mapping/impix/s1/S1_업무질의서_IMPIX.xlsx
+++ b/mapping/impix/s1/S1_업무질의서_IMPIX.xlsx
@@ -9,14 +9,16 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="업무질의서" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오별 집계" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="명사별 사용" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사건(정답지)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPI별 질의" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="명사별 사용" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사건(정답지)" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'업무질의서'!$A$1:$I$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'시나리오별 집계'!$A$1:$I$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'명사별 사용'!$A$1:$C$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'사건(정답지)'!$A$1:$D$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'업무질의서'!$A$1:$J$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'시나리오별 집계'!$A$1:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'KPI별 질의'!$A$1:$C$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'명사별 사용'!$A$1:$C$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'사건(정답지)'!$A$1:$D$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -458,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:J156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -467,9 +469,10 @@
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="34" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -505,15 +508,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>관련 KPI</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>기대 답(실습 데이터)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>S7 규칙 후보</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>S9 평가셋</t>
         </is>
@@ -550,13 +558,14 @@
           <t>BOMHeader, BOMLine, ItemMaster</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>버전 002(2026-07-01~), 자품목 9종(하우징·임펠러·모터·PCB·씰·O-링 2·볼트 4·커넥터·포장박스 0.1)</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -593,13 +602,14 @@
           <t>RoutingHeader, RoutingLine, Operation</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>주조 45초 → CNC 95초 → 세척 20초</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -636,13 +646,14 @@
           <t>OperationEquipment, Equipment, Operation</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>CNC-01~06 6대(CNC-06 사용여부 값 '1' 정규화 필요)</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -679,13 +690,14 @@
           <t>Equipment</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>DCM-01~04(도시바기계 2, LK 2), 구0호 DCM-00은 미사용</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -722,9 +734,10 @@
           <t>ItemMaster, CommonCodeMaster</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -761,13 +774,14 @@
           <t>ItemMaster</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -804,13 +818,14 @@
           <t>Plant, Line</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>P1 ML01 800EA, P2 AL01 600EA·AL02 300EA</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -847,17 +862,18 @@
           <t>BOMHeader, BOMLine, ItemMaster</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>1.02kg (B200 → HSG-B200 1EA → ALDC12 1.02kg)</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -894,13 +910,14 @@
           <t>ItemMaster, BOMLine, RoutingHeader</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -937,17 +954,18 @@
           <t>BOMLine, ItemMaster</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>EWP-B200 BOM 001 라인 9: IMP-B300</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -984,17 +1002,18 @@
           <t>ItemMaster</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>'EWP-A100 '(끝 공백), 'ewp-b200'(소문자)</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1031,9 +1050,10 @@
           <t>Equipment, Personnel, Department</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1070,9 +1090,10 @@
           <t>ItemMaster</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1109,9 +1130,10 @@
           <t>ItemMaster</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1148,13 +1170,14 @@
           <t>Operation</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>P100↔WDC10, P200↔WMC20, P300↔WWS30, A100↔WAS40, A200↔WLT50, A300↔WFI60, A400↔WPK70</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1191,17 +1214,18 @@
           <t>ItemMaster, UOMGroupLine</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>IMP-B200 'ea', MTR-24V '개'</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1238,9 +1262,10 @@
           <t>Operation, CommonCodeMaster</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1277,13 +1302,14 @@
           <t>Personnel, Equipment, OperationStart</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1320,17 +1346,18 @@
           <t>BOMHeader, BOMLine</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>CON-3P(커넥터), BOX-EWP(포장박스)</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1367,13 +1394,14 @@
           <t>Plant</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>1100·IMP1 → P1, 1200·IMP2 → P2</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1410,13 +1438,14 @@
           <t>Lot, Operation</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>E261020A2·E261020B1, 누설시험 완료 후 최종검사 대기</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1453,13 +1482,14 @@
           <t>ProductionOrder, Lot, OperationEnd</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1496,9 +1526,10 @@
           <t>OperationEnd, ProductionPerformance</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1535,17 +1566,18 @@
           <t>ProductionOrder, Lot, OperationEnd</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>MO261003001·05001·06001·07001: 보류 LOT으로 완성 193~195/400EA. MO260925001(193/400)·MO261008002(0/200)는 LOT 오더번호 오류(MO260999001)로 미완성처럼 보임 → 원천 정정 필요</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1582,9 +1614,10 @@
           <t>OperationStart, OperationEnd, RoutingLine</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1621,17 +1654,18 @@
           <t>Lot, OperationStart, Equipment</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>H261007A1, DCM-02(10-06 07:00 주조)</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1668,17 +1702,18 @@
           <t>Lot, OperationEnd, ProductionPerformanceQuality</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>E261003A1 6.8%, E261005A1 8.9%, E261006A1 9.5%, E261007A1 9.4%(모두 누설시험)</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1715,9 +1750,10 @@
           <t>OperationStart, Personnel</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1754,9 +1790,10 @@
           <t>ProductionOrder, OperationEnd</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1793,17 +1830,18 @@
           <t>OperationStart, OperationEnd</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>없음(진행 중 LOT은 다음 공정 착공 전)</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1840,17 +1878,18 @@
           <t>OperationStart, OperationEnd</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>E261009A2 누설시험(완공 14:52 &lt; 착공 14:57)</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1887,17 +1926,18 @@
           <t>OperationStart, OperationEnd</t>
         </is>
       </c>
-      <c r="G33" s="3" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>E260925B1 조립·누설시험 2건</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1934,17 +1974,18 @@
           <t>Lot, ProductionOrder</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>H260925A2·E260925A2·E261008B1(MO260999001)</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -1981,9 +2022,10 @@
           <t>Line, OperationEnd, ProductionPerformance</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr"/>
-      <c r="I35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2020,13 +2062,14 @@
           <t>OperationStart, OperationEnd, RoutingLine</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2063,9 +2106,10 @@
           <t>OperationStart, Equipment</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr"/>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2102,17 +2146,18 @@
           <t>ProductionOrder, Lot</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
         <is>
           <t>H260930B1 폐기(SCRAP)</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
       <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2149,9 +2194,10 @@
           <t>Lot, OperationEnd</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2188,13 +2234,14 @@
           <t>ProductionOrder, OperationStart</t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2231,13 +2278,14 @@
           <t>ProductionOrder</t>
         </is>
       </c>
-      <c r="G41" s="3" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>10-21~10-25 오더 8건(A100 400·B200 200씩)</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr"/>
-      <c r="I41" s="2" t="inlineStr">
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2246,45 +2294,46 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-01</t>
+          <t>Q-SC02-21</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>SC03 설비 파라미터 수집</t>
+          <t>SC02 착공·완공</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>진단</t>
+          <t>집계</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>DCM-02 금형온도가 규격 상한(240℃)을 넘은 기간과 최대값은?</t>
+          <t>10월(1~20일) 공정별 완공 양품 수량은?</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter &gt; USL</t>
+          <t>공정별 Σ 완공 양품(완공일 기준)</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter, EquipmentParameter</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-02 06:10 ~ 10-06 18:00, 574회, 최대 267.2℃</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
+          <t>OperationEnd, ProductionPerformance</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>PR01</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>P100 9,570 · P200 9,524 · P300 9,414 · A100 9,995 · A200 9,865 · A300 8,740 · A400 8,740EA</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2293,45 +2342,46 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-02</t>
+          <t>Q-SC02-22</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>SC03 설비 파라미터 수집</t>
+          <t>SC02 착공·완공</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>조회</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>금형온도 규격 이탈 중에 주조된 하우징 LOT은?</t>
+          <t>기준 시점(10-20 17:00) 재공 LOT과 수량·금액은?</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>이탈 시각이 주조 착공~완공 사이</t>
+          <t>LOT 상태 W·R·H, 수량 × 표준원가</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter, OperationStart, OperationEnd, Lot</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>H261003A1·H261005A1·H261006A1·H261007A1</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>PR02</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>6 LOT 1,086EA 61,542,000원 — 보류 4 LOT(E261003A1·05A1·06A1·07A1) 698EA, 대기 2 LOT(E261020A2·B1) 388EA</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2340,41 +2390,50 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-03</t>
+          <t>Q-SC02-23</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>SC03 설비 파라미터 수집</t>
+          <t>SC02 착공·완공</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>조회</t>
+          <t>진단</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>핵심(A등급) 파라미터와 규격은?</t>
+          <t>MES에서는 보류(H)인데 ERP에서 입고·출하된 LOT은?</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>ParameterGrade=CRITICAL</t>
+          <t>MES LotState=H ∩ ERP 생산입고·출하 LOT</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>EquipmentParameter</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>금형온도 180~240℃, 사출압력 600~900bar, 누설량 0~2.0cc/min</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr"/>
+          <t>Lot, ProductIncoming, ProductRelease</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>PR02, QM03</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>E261003A1 179EA — 10-08 ERP 수기 특채 입고(PR261008SP1) 후 같은 날 C001 출하(SO260928001). 시스템 간 상태 불일치</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2383,12 +2442,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-04</t>
+          <t>Q-SC02-24</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>SC03 설비 파라미터 수집</t>
+          <t>SC02 착공·완공</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2398,22 +2457,31 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>설비별 파라미터 수집 누락률은?</t>
+          <t>월별 제품 생산계획준수율은? 10월이 낮은 이유는?</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>NULL·공백 구간 / 기대 수집 건수</t>
+          <t>Σ min(일 입고, 일 계획) / Σ 일 계획</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter, EquipmentParameter</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr"/>
-      <c r="I45" s="2" t="inlineStr">
+          <t>ProductionPlanning, ProductIncoming</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>SC03</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>8월 93.10%, 9월 94.51%, 10월 89.11%(A100 85.08% — 보류 LOT으로 10-03~07 포장 양품 절반)</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2422,45 +2490,46 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-05</t>
+          <t>Q-SC02-25</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>SC03 설비 파라미터 수집</t>
+          <t>SC02 착공·완공</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>진단</t>
+          <t>집계</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>10-10 DCM-03 데이터 공백 구간과 원인은?</t>
+          <t>10월 완제품 제조 리드타임(조립~포장, 주조~포장)은?</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>수집 간격 &gt; 30분, 같은 시각 알람</t>
+          <t>FG LOT 조립 착공 → 포장 완공, 연결 하우징 주조 착공 → 포장 완공</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter, Alarm</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>02:00~06:00, PLC 통신 끊김(A900)</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
+          <t>Lot, OperationStart, OperationEnd</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>SC05</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>A100 6.91h / 37.80h, B200 8.42h / 37.25h</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2469,7 +2538,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-06</t>
+          <t>Q-SC03-01</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2484,12 +2553,12 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>CNC-03 진동이 관리상한(3.5mm/s)을 넘기 시작한 시점과 횟수는?</t>
+          <t>DCM-02 금형온도가 규격 상한(240℃)을 넘은 기간과 최대값은?</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter &gt; UCL</t>
+          <t>TraceParameter &gt; USL</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -2497,17 +2566,18 @@
           <t>TraceParameter, EquipmentParameter</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-14 00:10부터, 71회</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-02 06:10 ~ 10-06 18:00, 574회, 최대 267.2℃</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2516,7 +2586,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-07</t>
+          <t>Q-SC03-02</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2526,35 +2596,36 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>진단</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>LKT-02 누설량의 비정상 스파이크와 원인은?</t>
+          <t>금형온도 규격 이탈 중에 주조된 하우징 LOT은?</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>규격의 10배 초과 값</t>
+          <t>이탈 시각이 주조 착공~완공 사이</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
-        <is>
-          <t>10-11 09:00~10:00 7건, 단위 오류(×1000)</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>TraceParameter, OperationStart, OperationEnd, Lot</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>H261003A1·H261005A1·H261006A1·H261007A1</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2563,7 +2634,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-08</t>
+          <t>Q-SC03-03</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2573,31 +2644,32 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>진단</t>
+          <t>조회</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>LOT별 평균 금형온도와 해당 하우징 기공 불량률의 관계는?</t>
+          <t>핵심(A등급) 파라미터와 규격은?</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>주조 구간 평균 vs D-PORO 비율</t>
+          <t>ParameterGrade=CRITICAL</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter, Lot, ProductionPerformanceQuality</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
+          <t>EquipmentParameter</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>금형온도 180~240℃, 사출압력 600~900bar, 누설량 0~2.0cc/min</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2606,7 +2678,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-09</t>
+          <t>Q-SC03-04</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2621,22 +2693,23 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>다이캐스팅기 4대의 일평균 금형온도 추이는?</t>
+          <t>설비별 파라미터 수집 누락률은?</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>설비·일자별 평균</t>
+          <t>NULL·공백 구간 / 기대 수집 건수</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter, Equipment</t>
-        </is>
-      </c>
-      <c r="G50" s="3" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="2" t="inlineStr">
+          <t>TraceParameter, EquipmentParameter</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2645,7 +2718,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-10</t>
+          <t>Q-SC03-05</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2660,30 +2733,31 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>같은 파라미터인데 단위 표기가 다른 항목은?</t>
+          <t>10-10 DCM-03 데이터 공백 구간과 원인은?</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>ParameterUOMCode 표준화</t>
+          <t>수집 간격 &gt; 30분, 같은 시각 알람</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>EquipmentParameter, UOMGroupLine</t>
-        </is>
-      </c>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>DCM-04 금형온도 'degC', CNC-06 진동 'mm/sec'</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>TraceParameter, Alarm</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>02:00~06:00, PLC 통신 끊김(A900)</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2692,7 +2766,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-11</t>
+          <t>Q-SC03-06</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2702,17 +2776,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>집계</t>
+          <t>진단</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>관리한계(UCL·LCL) 이탈이 가장 많은 파라미터는?</t>
+          <t>CNC-03 진동이 관리상한(3.5mm/s)을 넘기 시작한 시점과 횟수는?</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>UCL/LCL 이탈 건수</t>
+          <t>TraceParameter &gt; UCL</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -2720,9 +2794,18 @@
           <t>TraceParameter, EquipmentParameter</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-14 00:10부터, 71회</t>
+        </is>
+      </c>
       <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2731,7 +2814,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-12</t>
+          <t>Q-SC03-07</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2746,26 +2829,31 @@
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>누설량 평균이 높은 날과 누설 불량률은 같이 움직이는가?</t>
+          <t>LKT-02 누설량의 비정상 스파이크와 원인은?</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>일별 LEAK_RATE 평균 vs A200 불량률</t>
+          <t>규격의 10배 초과 값</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter, ProductionPerformanceQuality</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>TraceParameter</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>10-11 09:00~10:00 7건, 단위 오류(×1000)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2774,7 +2862,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-13</t>
+          <t>Q-SC03-08</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2784,27 +2872,32 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>집계</t>
+          <t>진단</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>세척수 온도가 규격(50~70℃)을 벗어난 건수는?</t>
+          <t>LOT별 평균 금형온도와 해당 하우징 기공 불량률의 관계는?</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter 규격 판정</t>
+          <t>주조 구간 평균 vs D-PORO 비율</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter</t>
-        </is>
-      </c>
-      <c r="G54" s="3" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr"/>
+          <t>TraceParameter, Lot, ProductionPerformanceQuality</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2813,7 +2906,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-14</t>
+          <t>Q-SC03-09</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2823,31 +2916,28 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>집계</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>완제품 LOT E261006A1의 하우징이 주조될 때 금형온도 평균은?</t>
+          <t>다이캐스팅기 4대의 일평균 금형온도 추이는?</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>LOT 계보 → 주조 구간 → 파라미터 평균</t>
+          <t>설비·일자별 평균</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Lot, OperationStart, TraceParameter</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
+          <t>TraceParameter, Equipment</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2856,7 +2946,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-15</t>
+          <t>Q-SC03-10</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2871,26 +2961,31 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>수집 주기(600초)와 실제 수집 간격이 다른 설비는?</t>
+          <t>같은 파라미터인데 단위 표기가 다른 항목은?</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>연속 수집 간격 분포</t>
+          <t>ParameterUOMCode 표준화</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter, EquipmentParameter</t>
-        </is>
-      </c>
-      <c r="G56" s="3" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>EquipmentParameter, UOMGroupLine</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>DCM-04 금형온도 'degC', CNC-06 진동 'mm/sec'</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2899,7 +2994,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-16</t>
+          <t>Q-SC03-11</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -2909,31 +3004,28 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>집계</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>체결토크가 규격 하한 미만인 시점과 해당 조립 LOT은?</t>
+          <t>관리한계(UCL·LCL) 이탈이 가장 많은 파라미터는?</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>토크 &lt; LSL, 조립 구간 LOT</t>
+          <t>UCL/LCL 이탈 건수</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter, OperationStart, Lot</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
+          <t>TraceParameter, EquipmentParameter</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2942,7 +3034,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-17</t>
+          <t>Q-SC03-12</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -2952,27 +3044,32 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>집계</t>
+          <t>진단</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>다이캐스팅 사이클타임 평균은 표준(라우팅)과 어떻게 다른가?</t>
+          <t>누설량 평균이 높은 날과 누설 불량률은 같이 움직이는가?</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>CYCLE_T 평균 vs RunTime</t>
+          <t>일별 LEAK_RATE 평균 vs A200 불량률</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter, RoutingLine</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr"/>
+          <t>TraceParameter, ProductionPerformanceQuality</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -2981,7 +3078,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-18</t>
+          <t>Q-SC03-13</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -2991,17 +3088,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>진단</t>
+          <t>집계</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>최근 7일 연속 상승 추세를 보이는 파라미터는?</t>
+          <t>세척수 온도가 규격(50~70℃)을 벗어난 건수는?</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>일평균 기울기·런 규칙</t>
+          <t>TraceParameter 규격 판정</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -3009,13 +3106,10 @@
           <t>TraceParameter</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3024,7 +3118,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-19</t>
+          <t>Q-SC03-14</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3034,27 +3128,32 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>집계</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>규격 이탈 측정값을 검증결과코드로 분류하면 몇 건씩인가?</t>
+          <t>완제품 LOT E261006A1의 하우징이 주조될 때 금형온도 평균은?</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>OVER_USL / UNDER_LSL / NO_DATA</t>
+          <t>LOT 계보 → 주조 구간 → 파라미터 평균</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter, CommonCodeMaster</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr"/>
+          <t>Lot, OperationStart, TraceParameter</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3063,7 +3162,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Q-SC03-20</t>
+          <t>Q-SC03-15</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3078,30 +3177,27 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>금형온도 이상 전 24시간에 점진 상승 징후가 있었나?</t>
+          <t>수집 주기(600초)와 실제 수집 간격이 다른 설비는?</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>이상 시작 전 구간 추세</t>
+          <t>연속 수집 간격 분포</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>징후 없음: 직전 24시간 평균 210℃·최대 225℃(정상), 10-02 06:00에 237℃로 급등 후 계속 상승</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>TraceParameter, EquipmentParameter</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr"/>
       <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3110,37 +3206,42 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-01</t>
+          <t>Q-SC03-16</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SC04 설비 상태 변경</t>
+          <t>SC03 설비 파라미터 수집</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>집계</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>10월 설비별 가동률(가동시간/계획시간)은?</t>
+          <t>체결토크가 규격 하한 미만인 시점과 해당 조립 LOT은?</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>상태 가동 / (전체 - 비가동 계획)</t>
+          <t>토크 &lt; LSL, 조립 구간 LOT</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>EquipmentState, Equipment</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr"/>
+          <t>TraceParameter, OperationStart, Lot</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr"/>
       <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3149,12 +3250,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-02</t>
+          <t>Q-SC03-17</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SC04 설비 상태 변경</t>
+          <t>SC03 설비 파라미터 수집</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3164,26 +3265,23 @@
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>고장 건수와 정지시간이 가장 많은 설비는?</t>
+          <t>다이캐스팅 사이클타임 평균은 표준(라우팅)과 어떻게 다른가?</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>상태 고장 구간 합</t>
+          <t>CYCLE_T 평균 vs RunTime</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>EquipmentState, Equipment</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="inlineStr">
-        <is>
-          <t>정지시간 DCM-02 4시간 38분(4건). 건수는 WSH-01·CNC-05도 4건</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="2" t="inlineStr">
+          <t>TraceParameter, RoutingLine</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3192,12 +3290,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-03</t>
+          <t>Q-SC03-18</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SC04 설비 상태 변경</t>
+          <t>SC03 설비 파라미터 수집</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3207,30 +3305,27 @@
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>DCM-02 고장의 원인 코드와 정지시간은?</t>
+          <t>최근 7일 연속 상승 추세를 보이는 파라미터는?</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>고장 구간의 오류코드</t>
+          <t>일평균 기울기·런 규칙</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>EquipmentState, Alarm</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t>E03 온도이상 2건(10-04 1.5h, 10-05 1h10m), E06·E01 각 1건</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>TraceParameter</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3239,41 +3334,38 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-04</t>
+          <t>Q-SC03-19</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SC04 설비 상태 변경</t>
+          <t>SC03 설비 파라미터 수집</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>조회</t>
+          <t>집계</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>현재 설비 상태와 미해제 알람은?</t>
+          <t>규격 이탈 측정값을 검증결과코드로 분류하면 몇 건씩인가?</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>최신 상태, 해제 일시 없음</t>
+          <t>OVER_USL / UNDER_LSL / NO_DATA</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>EquipmentState, Alarm</t>
-        </is>
-      </c>
-      <c r="G65" s="3" t="inlineStr">
-        <is>
-          <t>미해제 알람: CNC-03 진동 경고(A202, 10-15 14:20)</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="2" t="inlineStr">
+          <t>TraceParameter, CommonCodeMaster</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3282,37 +3374,46 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-05</t>
+          <t>Q-SC03-20</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SC04 설비 상태 변경</t>
+          <t>SC03 설비 파라미터 수집</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>집계</t>
+          <t>진단</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>오류코드별 고장 건수는?</t>
+          <t>금형온도 이상 전 24시간에 점진 상승 징후가 있었나?</t>
         </is>
       </c>
       <c r="E66" s="3" t="inlineStr">
         <is>
-          <t>EquipmentErrorCode 표준 대응 후 집계</t>
+          <t>이상 시작 전 구간 추세</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>EquipmentState, CommonCodeMaster</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr"/>
+          <t>TraceParameter</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>징후 없음: 직전 24시간 평균 210℃·최대 225℃(정상), 10-02 06:00에 237℃로 급등 후 계속 상승</t>
+        </is>
+      </c>
       <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3321,7 +3422,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-06</t>
+          <t>Q-SC04-01</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3331,31 +3432,28 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>조회</t>
+          <t>집계</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>계획보전 실시 주기와 1회 시간은?</t>
+          <t>10월 설비별 가동률(가동시간/계획시간)은?</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>상태 보전 구간</t>
+          <t>상태 가동 / (전체 - 비가동 계획)</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>EquipmentState</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>매주 토요일 19:00~21:00(2시간)</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr">
+          <t>EquipmentState, Equipment</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3364,7 +3462,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-07</t>
+          <t>Q-SC04-02</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3374,31 +3472,32 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>진단</t>
+          <t>집계</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>고장 직전 30분 안에 발생한 알람 유형은?</t>
+          <t>고장 건수와 정지시간이 가장 많은 설비는?</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
         <is>
-          <t>고장 시작 - 30분 ~ 고장 시작</t>
+          <t>상태 고장 구간 합</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>EquipmentState, Alarm</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
+          <t>EquipmentState, Equipment</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>정지시간 DCM-02 4시간 38분(4건). 건수는 WSH-01·CNC-05도 4건</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3407,7 +3506,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-08</t>
+          <t>Q-SC04-03</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3417,27 +3516,36 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>집계</t>
+          <t>진단</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>금형온도 상한 초과 알람(A101)의 발생 횟수와 시간대 분포는?</t>
+          <t>DCM-02 고장의 원인 코드와 정지시간은?</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>알람 코드·시간대별 집계</t>
+          <t>고장 구간의 오류코드</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Alarm</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr"/>
+          <t>EquipmentState, Alarm</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>E03 온도이상 2건(10-04 1.5h, 10-05 1h10m), E06·E01 각 1건</t>
+        </is>
+      </c>
       <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3446,7 +3554,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-09</t>
+          <t>Q-SC04-04</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3456,27 +3564,32 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>집계</t>
+          <t>조회</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>설비별 MTBF·MTTR은?</t>
+          <t>현재 설비 상태와 미해제 알람은?</t>
         </is>
       </c>
       <c r="E70" s="3" t="inlineStr">
         <is>
-          <t>가동시간/고장횟수, 고장시간/고장횟수</t>
+          <t>최신 상태, 해제 일시 없음</t>
         </is>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>EquipmentState</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr"/>
-      <c r="I70" s="2" t="inlineStr">
+          <t>EquipmentState, Alarm</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>미해제 알람: CNC-03 진동 경고(A202, 10-15 14:20)</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3485,7 +3598,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-10</t>
+          <t>Q-SC04-05</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3495,31 +3608,28 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>진단</t>
+          <t>집계</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>대기시간이 긴 설비와 대기가 생기는 시간대는?</t>
+          <t>오류코드별 고장 건수는?</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>상태 대기 구간</t>
+          <t>EquipmentErrorCode 표준 대응 후 집계</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>EquipmentState</t>
-        </is>
-      </c>
-      <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
+          <t>EquipmentState, CommonCodeMaster</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3528,7 +3638,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-11</t>
+          <t>Q-SC04-06</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3538,17 +3648,17 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>진단</t>
+          <t>조회</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>상태 구간이 겹치는 기록은?</t>
+          <t>계획보전 실시 주기와 1회 시간은?</t>
         </is>
       </c>
       <c r="E72" s="3" t="inlineStr">
         <is>
-          <t>같은 설비의 구간 교차</t>
+          <t>상태 보전 구간</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -3556,17 +3666,14 @@
           <t>EquipmentState</t>
         </is>
       </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>5건: WSH-01 토요일 가동·보전 겹침 4건, CNC-03 10-16 고장·가동 겹침 1건</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>매주 토요일 19:00~21:00(2시간)</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3575,7 +3682,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-12</t>
+          <t>Q-SC04-07</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3585,31 +3692,32 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>진단</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>고장 중에 처리되던 LOT은?</t>
+          <t>고장 직전 30분 안에 발생한 알람 유형은?</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>고장 구간과 착공~완공 교차</t>
+          <t>고장 시작 - 30분 ~ 고장 시작</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>EquipmentState, OperationStart, Lot</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>EquipmentState, Alarm</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3618,7 +3726,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-13</t>
+          <t>Q-SC04-08</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3633,22 +3741,23 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>알람이 가장 많은 공정은?</t>
+          <t>금형온도 상한 초과 알람(A101)의 발생 횟수와 시간대 분포는?</t>
         </is>
       </c>
       <c r="E74" s="3" t="inlineStr">
         <is>
-          <t>알람 설비의 공정</t>
+          <t>알람 코드·시간대별 집계</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Alarm, Equipment, Operation</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="2" t="inlineStr">
+          <t>Alarm</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3657,7 +3766,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-14</t>
+          <t>Q-SC04-09</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3672,12 +3781,12 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>제어모드(원격·로컬)별 운전 비율은?</t>
+          <t>설비별 MTBF·MTTR은?</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>EquipmentControlMode 대응</t>
+          <t>가동시간/고장횟수, 고장시간/고장횟수</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -3685,9 +3794,10 @@
           <t>EquipmentState</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr"/>
-      <c r="I75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3696,7 +3806,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-15</t>
+          <t>Q-SC04-10</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3706,17 +3816,17 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>집계</t>
+          <t>진단</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>비가동 계획을 뺀 실가동률은?</t>
+          <t>대기시간이 긴 설비와 대기가 생기는 시간대는?</t>
         </is>
       </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>가동 / (전체 - 비가동 계획 - 보전)</t>
+          <t>상태 대기 구간</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -3724,9 +3834,14 @@
           <t>EquipmentState</t>
         </is>
       </c>
-      <c r="G76" s="3" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3735,7 +3850,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-16</t>
+          <t>Q-SC04-11</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3745,35 +3860,36 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>진단</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>CNC-03 진동 상승 이후 공구마모 고장까지 얼마나 걸렸나?</t>
+          <t>상태 구간이 겹치는 기록은?</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>진동 UCL 초과 시작 → 고장 E07</t>
+          <t>같은 설비의 구간 교차</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>TraceParameter, EquipmentState</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>약 58시간(10-14 00:10 → 10-16 10:15)</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>EquipmentState</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>5건: WSH-01 토요일 가동·보전 겹침 4건, CNC-03 10-16 고장·가동 겹침 1건</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3782,7 +3898,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-17</t>
+          <t>Q-SC04-12</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3792,27 +3908,32 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>집계</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>중대(H) 알람의 평균 해제 시간은?</t>
+          <t>고장 중에 처리되던 LOT은?</t>
         </is>
       </c>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>해제-발생 평균</t>
+          <t>고장 구간과 착공~완공 교차</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Alarm</t>
-        </is>
-      </c>
-      <c r="G78" s="3" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr"/>
+          <t>EquipmentState, OperationStart, Lot</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="3" t="inlineStr"/>
       <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3821,7 +3942,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-18</t>
+          <t>Q-SC04-13</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -3831,35 +3952,28 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>진단</t>
+          <t>집계</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>셋업 상태 기록이 있는가? 없다면 무엇으로 대신하나?</t>
+          <t>알람이 가장 많은 공정은?</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>상태 셋업 존재 여부</t>
+          <t>알람 설비의 공정</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>EquipmentState</t>
-        </is>
-      </c>
-      <c r="G79" s="3" t="inlineStr">
-        <is>
-          <t>셋업(5) 기록 없음 → 원천 공백, 대기로 기록됨</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr">
+          <t>Alarm, Equipment, Operation</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3868,7 +3982,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-19</t>
+          <t>Q-SC04-14</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -3883,22 +3997,23 @@
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>설비 그룹별(DCM·CNC·…) 고장 빈도는?</t>
+          <t>제어모드(원격·로컬)별 운전 비율은?</t>
         </is>
       </c>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>설비 소분류별 고장 건수</t>
+          <t>EquipmentControlMode 대응</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>EquipmentState, Equipment</t>
-        </is>
-      </c>
-      <c r="G80" s="3" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="2" t="inlineStr">
+          <t>EquipmentState</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="3" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3907,7 +4022,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Q-SC04-20</t>
+          <t>Q-SC04-15</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -3917,31 +4032,28 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>진단</t>
+          <t>집계</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>고장이 잦은 설비가 처리한 LOT의 불량률이 더 높은가?</t>
+          <t>비가동 계획을 뺀 실가동률은?</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>설비별 고장 건수 vs 처리 LOT 불량률</t>
+          <t>가동 / (전체 - 비가동 계획 - 보전)</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>EquipmentState, OperationEnd, ProductionPerformanceQuality</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
+          <t>EquipmentState</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="3" t="inlineStr"/>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3950,41 +4062,46 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-01</t>
+          <t>Q-SC04-16</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SC05 품질 실적</t>
+          <t>SC04 설비 상태 변경</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>집계</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>10월 공정별 불량률(PPM)은?</t>
+          <t>CNC-03 진동 상승 이후 공구마모 고장까지 얼마나 걸렸나?</t>
         </is>
       </c>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>불량수량/검사수량 × 10⁶</t>
+          <t>진동 UCL 초과 시작 → 고장 E07</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>ProductionPerformanceQuality</t>
-        </is>
-      </c>
-      <c r="G82" s="3" t="inlineStr">
-        <is>
-          <t>세척·외관 11,125, 누설시험 10,991, CNC 4,819, 최종검사 4,693</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr"/>
+          <t>TraceParameter, EquipmentState</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>약 58시간(10-14 00:10 → 10-16 10:15)</t>
+        </is>
+      </c>
       <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3993,12 +4110,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-02</t>
+          <t>Q-SC04-17</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SC05 품질 실적</t>
+          <t>SC04 설비 상태 변경</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4008,26 +4125,23 @@
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>불량 유형별 수량 순위는?</t>
+          <t>중대(H) 알람의 평균 해제 시간은?</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>불량유형코드별 합계</t>
+          <t>해제-발생 평균</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>ProductionPerformanceQuality</t>
-        </is>
-      </c>
-      <c r="G83" s="3" t="inlineStr">
-        <is>
-          <t>누설 166, 스크래치 126, 치수 74, 이음 63, 기공 26, 버 18, 작동 2</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="2" t="inlineStr">
+          <t>Alarm</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4036,12 +4150,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-03</t>
+          <t>Q-SC04-18</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SC05 품질 실적</t>
+          <t>SC04 설비 상태 변경</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4051,30 +4165,31 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>누설 불량이 급증한 날과 영향 LOT은?</t>
+          <t>셋업 상태 기록이 있는가? 없다면 무엇으로 대신하나?</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>일별 누설 불량률 &gt; 3% 또는 LOT별 &gt; 5%</t>
+          <t>상태 셋업 존재 여부</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>ProductionPerformanceQuality, Lot</t>
-        </is>
-      </c>
-      <c r="G84" s="3" t="inlineStr">
-        <is>
-          <t>일별 3% 초과: 10-05·06·07. LOT별 5% 초과: E261003A1·E261005A1·E261006A1·E261007A1</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>EquipmentState</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>셋업(5) 기록 없음 → 원천 공백, 대기로 기록됨</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4083,45 +4198,38 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-04</t>
+          <t>Q-SC04-19</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SC05 품질 실적</t>
+          <t>SC04 설비 상태 변경</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>진단</t>
+          <t>집계</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>누설 불량 급증의 근본 원인은?</t>
+          <t>설비 그룹별(DCM·CNC·…) 고장 빈도는?</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>LOT 계보 → 주조 설비 → 파라미터 이상 연결</t>
+          <t>설비 소분류별 고장 건수</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>ProductionPerformanceQuality, Lot, OperationStart, TraceParameter, Alarm</t>
-        </is>
-      </c>
-      <c r="G85" s="3" t="inlineStr">
-        <is>
-          <t>DCM-02 금형온도 상승(10-02~06) → 하우징 기공 → 조립 후 누설</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
+          <t>EquipmentState, Equipment</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="3" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4130,45 +4238,42 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-05</t>
+          <t>Q-SC04-20</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SC05 품질 실적</t>
+          <t>SC04 설비 상태 변경</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>진단</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>기공 불량이 난 하우징 LOT과 주조 설비는?</t>
+          <t>고장이 잦은 설비가 처리한 LOT의 불량률이 더 높은가?</t>
         </is>
       </c>
       <c r="E86" s="3" t="inlineStr">
         <is>
-          <t>D-PORO 검사 LOT → 주조 착공 설비</t>
+          <t>설비별 고장 건수 vs 처리 LOT 불량률</t>
         </is>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>ProductionPerformanceQuality, Lot, OperationStart</t>
-        </is>
-      </c>
-      <c r="G86" s="3" t="inlineStr">
-        <is>
-          <t>H261003A1·H261005A1(6EA), H261006A1·H261007A1(7EA), 모두 DCM-02</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+          <t>EquipmentState, OperationEnd, ProductionPerformanceQuality</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="3" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4177,45 +4282,46 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-06</t>
+          <t>Q-SC04-21</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SC05 품질 실적</t>
+          <t>SC04 설비 상태 변경</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>판단</t>
+          <t>집계</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>보류 LOT이 속한 제조오더와 납기 영향은?</t>
+          <t>10월 설비별 OEE 하위 3대는?</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>LOT → 생산지시 → 생산완료기한</t>
+          <t>시간가동율 × 성능가동율 × 양품율</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Lot, ProductionOrder</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t>MO261003001·05001·06001·07001, 05~07은 긴급 납기 단축 오더</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
+          <t>EquipmentState, OperationEnd, RoutingLine</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>EQ08, EQ02, EQ06, EQ07</t>
+        </is>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>WSH-01 88.52%(양품율 98.85%), LKT-02 89.08%, DCM-02 89.28% — 공장 전체 96.18%</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4224,37 +4330,46 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-07</t>
+          <t>Q-SC04-22</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>SC05 품질 실적</t>
+          <t>SC04 설비 상태 변경</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>조회</t>
+          <t>집계</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>판정이 NG인 검사와 LOT은?</t>
+          <t>10월 DCM-02의 시간가동율·MTBF·MTTR은?</t>
         </is>
       </c>
       <c r="E88" s="3" t="inlineStr">
         <is>
-          <t>검사 판정 NG(불량률 3% 초과)</t>
+          <t>상태 구간(고장 3) 기준</t>
         </is>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>ProductionPerformanceQuality, Lot</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr"/>
-      <c r="I88" s="2" t="inlineStr">
+          <t>EquipmentState</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>EQ06, EQ04, EQ05</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>시간가동율 89.62%, MTBF 10.0시간(고장 4건), MTTR 69.5분(E03 2건·E06·E01)</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4263,37 +4378,50 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-08</t>
+          <t>Q-SC04-23</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SC05 품질 실적</t>
+          <t>SC04 설비 상태 변경</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>집계</t>
+          <t>진단</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>품목별(A100·B200) 종합 수율은?</t>
+          <t>성능가동율이 100%를 넘는 설비와 그 의미는?</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>포장 양품 / 주조 투입</t>
+          <t>Σ(처리수량 × 표준시간) / 가동시간 &gt; 100%</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>ProductionPerformance, ItemMaster</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr"/>
+          <t>RoutingLine, EquipmentState</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>EQ07</t>
+        </is>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>LKT-01 102.72%, CNC-01 100.95%, CNC-04 100.69% — 표준 작업시간이 실제보다 느슨함(기준 재설정 대상)</t>
+        </is>
+      </c>
       <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4302,12 +4430,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-09</t>
+          <t>Q-SC04-24</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SC05 품질 실적</t>
+          <t>SC04 설비 상태 변경</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -4317,22 +4445,31 @@
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>CNC 공정 치수불량 추이는?</t>
+          <t>10월 LKT-02의 표준 UPM 대비 분당 생산성은?</t>
         </is>
       </c>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>P200 D-DIM 일별</t>
+          <t>실제 UPM(처리수량 / LOT 처리시간) ÷ 표준 UPM(60/표준초)</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>ProductionPerformanceQuality</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr"/>
-      <c r="I90" s="2" t="inlineStr">
+          <t>OperationStart, OperationEnd, RoutingLine</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>EQ01</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>93.26%(실제 1.60 / 표준 1.71 UPM)</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4341,45 +4478,46 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-10</t>
+          <t>Q-SC04-25</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>SC05 품질 실적</t>
+          <t>SC04 설비 상태 변경</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>진단</t>
+          <t>집계</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>표준 불량유형코드로 대응되지 않는 불량 코드는?</t>
+          <t>10월 설비별 작업시간(가동시간) 상위 3대는?</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>DefectTypeCode/DetailCode 대응표</t>
+          <t>상태 1(가동) 시간 합계</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>ProductionPerformanceQuality, CommonCodeMaster</t>
-        </is>
-      </c>
-      <c r="G91" s="3" t="inlineStr">
-        <is>
-          <t>D-PORO(기공), D-SHORT(미성형) → Extension 후보</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
+          <t>EquipmentState</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>EQ03</t>
+        </is>
+      </c>
+      <c r="H91" s="3" t="inlineStr">
+        <is>
+          <t>ASM-01 110.9시간, ASM-02 69.7시간, WSH-01 60.8시간</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4388,7 +4526,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-11</t>
+          <t>Q-SC05-01</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4403,12 +4541,12 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>일별 불량 PPM 추이는?</t>
+          <t>MES 기간(9-21~10-20) 검사 기준 공정별 불량률(PPM)은?</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>검사일 기준</t>
+          <t>검사 실적 불량수량/검사수량 × 10⁶(월별 완공 기준은 KPI QM05)</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -4416,9 +4554,14 @@
           <t>ProductionPerformanceQuality</t>
         </is>
       </c>
-      <c r="G92" s="3" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr"/>
-      <c r="I92" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>세척·외관 11,125, 누설시험 10,991, CNC 4,819, 최종검사 4,693</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4427,7 +4570,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-12</t>
+          <t>Q-SC05-02</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4442,12 +4585,12 @@
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>불량률 3%를 넘은 검사 건수는?</t>
+          <t>불량 유형별 수량 순위는?</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>검사별 불량률</t>
+          <t>불량유형코드별 합계</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -4455,9 +4598,14 @@
           <t>ProductionPerformanceQuality</t>
         </is>
       </c>
-      <c r="G93" s="3" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr"/>
-      <c r="I93" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="3" t="inlineStr">
+        <is>
+          <t>누설 166, 스크래치 126, 치수 74, 이음 63, 기공 26, 버 18, 작동 2</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4466,7 +4614,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-13</t>
+          <t>Q-SC05-03</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4476,27 +4624,36 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>집계</t>
+          <t>진단</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>검사자별 검사 건수와 불량 검출률은?</t>
+          <t>누설 불량이 급증한 날과 영향 LOT은?</t>
         </is>
       </c>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>검사자 기준</t>
+          <t>일별 누설 불량률 &gt; 3% 또는 LOT별 &gt; 5%</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>ProductionPerformanceQuality, Personnel</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr"/>
+          <t>ProductionPerformanceQuality, Lot</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>일별 3% 초과: 10-05·06·07. LOT별 5% 초과: E261003A1·E261005A1·E261006A1·E261007A1</t>
+        </is>
+      </c>
       <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4505,7 +4662,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-14</t>
+          <t>Q-SC05-04</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4520,26 +4677,31 @@
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>같은 날 만든 A100 완제품 LOT 두 개의 불량률 차이는 왜 생기나?</t>
+          <t>누설 불량 급증의 근본 원인은?</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>LOT별 하우징·설비 비교</t>
+          <t>LOT 계보 → 주조 설비 → 파라미터 이상 연결</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>Lot, OperationStart, ProductionPerformanceQuality</t>
-        </is>
-      </c>
-      <c r="G95" s="3" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>ProductionPerformanceQuality, Lot, OperationStart, TraceParameter, Alarm</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>DCM-02 금형온도 상승(10-02~06) → 하우징 기공 → 조립 후 누설</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4548,7 +4710,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-15</t>
+          <t>Q-SC05-05</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4558,27 +4720,36 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>집계</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>최종검사의 이음(소음) 불량 비율은?</t>
+          <t>기공 불량이 난 하우징 LOT과 주조 설비는?</t>
         </is>
       </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>A300 D-NOISE / 검사수량</t>
+          <t>D-PORO 검사 LOT → 주조 착공 설비</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>ProductionPerformanceQuality</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr"/>
+          <t>ProductionPerformanceQuality, Lot, OperationStart</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>H261003A1·H261005A1(6EA), H261006A1·H261007A1(7EA), 모두 DCM-02</t>
+        </is>
+      </c>
       <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4587,7 +4758,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-16</t>
+          <t>Q-SC05-06</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4597,31 +4768,36 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>판단</t>
         </is>
       </c>
       <c r="D97" s="3" t="inlineStr">
         <is>
-          <t>하우징 기공 불량이 조립 후 누설로 이어진 비율은?</t>
+          <t>보류 LOT이 속한 제조오더와 납기 영향은?</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>기공 발생 하우징 LOT의 하위 LOT 누설률</t>
+          <t>LOT → 생산지시 → 생산완료기한</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>Lot, ProductionPerformanceQuality</t>
-        </is>
-      </c>
-      <c r="G97" s="3" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>Lot, ProductionOrder</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>MO261003001·05001·06001·07001, 05~07은 긴급 납기 단축 오더</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4630,7 +4806,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-17</t>
+          <t>Q-SC05-07</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4640,35 +4816,28 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>진단</t>
+          <t>조회</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>DCM-02에서 주조한 하우징과 다른 설비 하우징의 누설 불량률 비교는?</t>
+          <t>판정이 NG인 검사와 LOT은?</t>
         </is>
       </c>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>주조 설비별 하위 LOT 누설률</t>
+          <t>검사 판정 NG(불량률 3% 초과)</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>Lot, OperationStart, ProductionPerformanceQuality</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t>DCM-02 1.93% vs 기타 0.68%</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
+          <t>ProductionPerformanceQuality, Lot</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="3" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4677,7 +4846,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-18</t>
+          <t>Q-SC05-08</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4687,35 +4856,28 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>진단</t>
+          <t>집계</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>B200의 누설 불량률이 A100보다 낮은 이유는?</t>
+          <t>품목별(A100·B200) 종합 수율은?</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>품목별 주조 설비 배분</t>
+          <t>포장 양품 / 주조 투입</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>Lot, OperationStart, Equipment</t>
-        </is>
-      </c>
-      <c r="G99" s="3" t="inlineStr">
-        <is>
-          <t>B200 하우징은 DCM-02에서 주조하지 않음</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
+          <t>ProductionPerformance, ItemMaster</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="3" t="inlineStr"/>
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4724,7 +4886,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Q-SC05-19</t>
+          <t>Q-SC05-09</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4734,31 +4896,28 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>조회</t>
+          <t>집계</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>폐기된 LOT과 수량은?</t>
+          <t>CNC 공정 치수불량 추이는?</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>LotState=SCRAP</t>
+          <t>P200 D-DIM 일별</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>Lot</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr">
-        <is>
-          <t>H260930B1 200EA(취소 오더)</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr"/>
-      <c r="I100" s="2" t="inlineStr">
+          <t>ProductionPerformanceQuality</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="3" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4767,44 +4926,2705 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>Q-SC05-10</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>SC05 품질 실적</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>표준 불량유형코드로 대응되지 않는 불량 코드는?</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>DefectTypeCode/DetailCode 대응표</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>ProductionPerformanceQuality, CommonCodeMaster</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>D-PORO(기공), D-SHORT(미성형) → Extension 후보</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC05-11</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>SC05 품질 실적</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>일별 불량 PPM 추이는?</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>검사일 기준</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>ProductionPerformanceQuality</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="3" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC05-12</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>SC05 품질 실적</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>불량률 3%를 넘은 검사 건수는?</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>검사별 불량률</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>ProductionPerformanceQuality</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="3" t="inlineStr"/>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC05-13</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>SC05 품질 실적</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>검사자별 검사 건수와 불량 검출률은?</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>검사자 기준</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>ProductionPerformanceQuality, Personnel</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="3" t="inlineStr"/>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC05-14</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>SC05 품질 실적</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>같은 날 만든 A100 완제품 LOT 두 개의 불량률 차이는 왜 생기나?</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>LOT별 하우징·설비 비교</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>Lot, OperationStart, ProductionPerformanceQuality</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="3" t="inlineStr"/>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC05-15</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>SC05 품질 실적</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>최종검사의 이음(소음) 불량 비율은?</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>A300 D-NOISE / 검사수량</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>ProductionPerformanceQuality</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="3" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC05-16</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>SC05 품질 실적</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>하우징 기공 불량이 조립 후 누설로 이어진 비율은?</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>기공 발생 하우징 LOT의 하위 LOT 누설률</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>Lot, ProductionPerformanceQuality</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="3" t="inlineStr"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC05-17</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>SC05 품질 실적</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>DCM-02에서 주조한 하우징과 다른 설비 하우징의 누설 불량률 비교는?</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>주조 설비별 하위 LOT 누설률</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>Lot, OperationStart, ProductionPerformanceQuality</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>DCM-02 1.93% vs 기타 0.68%</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC05-18</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>SC05 품질 실적</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>B200의 누설 불량률이 A100보다 낮은 이유는?</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>품목별 주조 설비 배분</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>Lot, OperationStart, Equipment</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>B200 하우징은 DCM-02에서 주조하지 않음</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC05-19</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>SC05 품질 실적</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>조회</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>폐기된 LOT과 수량은?</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>LotState=SCRAP</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>H260930B1 200EA(취소 오더)</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
           <t>Q-SC05-20</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>SC05 품질 실적</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
         <is>
           <t>요약</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>10월 품질 실적을 공정별 불량률과 주요 원인 3가지로 요약해 줘</t>
         </is>
       </c>
-      <c r="E101" s="3" t="inlineStr">
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>SC05-01·02·04 종합</t>
         </is>
       </c>
-      <c r="F101" s="3" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr">
         <is>
           <t>ProductionPerformanceQuality, Lot, TraceParameter</t>
         </is>
       </c>
-      <c r="G101" s="3" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr"/>
-      <c r="I101" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="3" t="inlineStr"/>
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC05-21</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>SC05 품질 실적</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>10월 공정 PPM 상위 3개 공정은?</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>완공 기준 Σ 불량 / Σ 처리수량 × 10⁶</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>OperationEnd, ProductionPerformanceQuality</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>QM05</t>
+        </is>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>A200 13,006, P300 11,550, P200 4,807 PPM</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC05-22</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>SC05 품질 실적</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>직행률(FPY)은 9월과 10월에 각각 얼마인가?</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>공정 양품율의 곱</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>OperationEnd</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>PR03</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>9월 96.96%, 10월 96.32%</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC05-23</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>SC05 품질 실적</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>10월 공정별 불량금액 1위 공정과 금액은?</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>Σ 폐기수량 × 공정 단계 단위원가</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>ProductionPerformanceQuality, GoodsIssue</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>PR04</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>A200(누설시험) 6,110,000원 — 전체 10,350,000원의 59%</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC05-24</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>SC05 품질 실적</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>10월 불량 유형별 폐기 금액 Top3는?</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>불량유형별 Σ 폐기금액</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>ProductionPerformanceQuality</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>QM06</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>D-LEAK 130EA 6,110,000원, D-NOISE 38EA 2,340,000원, D-SCR 73EA 804,200원</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC05-25</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>SC05 품질 실적</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>10월 누설 불량 폐기 금액이 9월보다 크게 늘어난 원인은?</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>QM06 누설 증가 → LOT 계보 → 주조 설비·파라미터</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>ProductionPerformanceQuality, Lot, TraceParameter</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>QM06, PR04</t>
+        </is>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>9월 1,692,000원 → 10월 6,110,000원. DCM-02 금형온도 상승(EV1) → 하우징 기공(EV2) → 조립 후 누설</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-01</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>9월·10월 고객 부적합 건수는?</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>클레임 발생일 기준 건수</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>Return, AfterSalesServiceRequest, CustomerPartyMaster</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>QM01</t>
+        </is>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>9월 3건(C001·C002·C003 각 1), 10월 4건(C001 2, C002 1, C003 1)</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-02</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>조회</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>10월 고객 라인 중단 클레임의 고객·LOT·손실금액은?</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>클레임 유형 LS</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>Return, Lot</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>QM03</t>
+        </is>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>CL2610-001 — C001, LOT E261003A1, 누수 6EA, 라인 40분 중단, 15,000,000원</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-03</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>CL2610-001 클레임 LOT의 생산 이력(하우징·주조 설비)은?</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>출하 LOT → LOT 계보 → 주조 착공 설비</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>Lot, OperationStart, ProductRelease</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>QM03, PR02</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>E261003A1(10-03 조립 ASM-01) ← 하우징 H261003A1(10-02 07:00 DCM-02 주조, 기공) → MES 보류 후 ERP 특채 출하(10-08)</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-04</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>10월 고객 부적합 일정 준수율과 미준수 건은?</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>회신 기한 도래 건 중 기한 내 회신 비율</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>CorrectiveActionRequest, CorrectiveActionResult</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>QM02</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>66.67%(4/6). 미준수: CL2609-002(기한 10-05, 회신 10-07), CL2610-002(기한 10-19, 미회신)</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-05</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>월별 필드 반송 건수는?</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>클레임 유형 FR</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>Return, AfterSalesServiceRequest</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>QM03</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>9월 1건(CL2609-002, LOT 미상), 10월 1건(CL2610-003, E261005A2)</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-06</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>LOT 추적이 안 되는 고객 클레임은?</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>클레임 LOT NULL 또는 MES LOT 없음</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>Return, Lot</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>QM01</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>CL2609-002(LOT 미기록), CL2609-001(E260915A1 — MES 도입 전 LOT, MES에 없음)</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-07</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>10월 Q-COST와 매출 대비 비율은?</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>Σ P+A+IF+EF / 매출액(출하 × 판매단가)</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="inlineStr">
+        <is>
+          <t>ProductRelease, SalesOrderLine</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>QM04</t>
+        </is>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>44,500,000원, 매출 713,346,000원 대비 6.24%(9월 2.56%)</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-08</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>10월 Q-COST 구성(P·A·IF·EF)은?</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>비용 구분별 합계</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>ProductRelease</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>QM04</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>예방 2,000,000 · 평가 14,100,000 · 내부실패 11,700,000 · 외부실패 16,700,000원</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-09</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>판단</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>10월 Q-COST가 급증한 주된 요인은?</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>비용 구분별 전월 대비 증가</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="inlineStr">
+        <is>
+          <t>Return, Lot</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>QM04, PR05</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="inlineStr">
+        <is>
+          <t>외부실패 1,570,000 → 16,700,000원. 클레임 16,390,000원 중 CL2610-001 라인 중단 15,000,000원(특채 출하 LOT)</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-10</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>10월 실패비용(내부·외부) 합계는?</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>IF + EF</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>Return</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>PR05</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>28,400,000원(내부 11,700,000, 외부 16,700,000)</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-11</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>10월 불량 손실액은?</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>Σ 폐기금액 + Σ 클레임 금액</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="inlineStr">
+        <is>
+          <t>ProductionPerformanceQuality, Return</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>QM07</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="inlineStr">
+        <is>
+          <t>26,740,000원(사내 폐기 10,350,000 + 고객 클레임 16,390,000)</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-12</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>협력업체별 부적합 건수(9월·10월)는?</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>부적합 발생일 기준 건수</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>CorrectiveActionRequest, VendorPartyMaster</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>QM08</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>9월 V001 1건·V003 3건, 10월 V003 1건</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-13</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>시정조치(CAR)가 완료되지 않은 협력업체 부적합은?</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>CAR 완료일 NULL</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="inlineStr">
+        <is>
+          <t>CorrectiveActionRequest, CorrectiveActionResult</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>QM08</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="inlineStr">
+        <is>
+          <t>NCR2609902(V003 CON-3P 고객 발견), NCR2610003(V003 PCB-EWP24 수입검사)</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-14</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>10월 수입검사 PPM과 LOT 불합격률은?</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>Σ 시료 불량 / Σ 시료 × 10⁶</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>SupplierInspectionResult, GoodsReceipt</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>QM09</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>3,942 PPM(6/1,522), LOT 불합격 1/29(3.4%)</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-15</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>조회</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>10월 수입검사 불합격 LOT과 처리는?</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>판정 R</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="inlineStr">
+        <is>
+          <t>SupplierInspectionResult, GoodsReceipt</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>QM09</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="inlineStr">
+        <is>
+          <t>PCB-EWP24(V003, 10-05 입고 980EA) 납땜 불량 5EA → 10-06 오후 대체 납품</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-16</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>PCB-EWP24 수입검사 불합격이 생산에 준 영향은?</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>불합격 → 가용재고 → 착수 점검</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>SupplierInspectionResult, AvailableInventory, ProductionOrder</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>QM09, SC04</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>MO261006002 착수 점검에서 PCB-EWP24 24EA 부족(10월 자재충족율 94.12%의 원인 중 하나)</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-17</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>CL2609-003(커넥터 접촉불량) 클레임과 연결되는 협력업체 이력은?</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>고객 불량 → 부품 → 협력업체 부적합·수입검사</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>Return, CorrectiveActionRequest, SupplierInspectionResult</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>QM08, QM01</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>V003 CON-3P: 9-21 수입검사 특채(S, 외관 2EA) → 9-27 라인 발견 6EA → 9-29 고객 발견 4EA(NCR2609902, CAR 미완료)</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-18</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>9월 협력업체별 수입검사 PPM 상위는?</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>협력업체별 시료 PPM</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>SupplierInspectionResult</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>QM09</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>V001 6,667, V003 5,000, V005 5,000 PPM</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-19</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>판단</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>협력업체 관리 우선순위 1위와 근거는?</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>부적합 건수·수입검사 PPM·CAR 미완료 종합</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>CorrectiveActionRequest, SupplierInspectionResult, VendorPartyMaster</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>QM08, QM09</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>V003 하늘전자 — 9~10월 부적합 4건, 10월 수입검사 10,000 PPM, CAR 미완료 2건, 고객 클레임 연결</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC06-20</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>클레임·품질비용 데이터는 KS X 9101 표준 명사에 어떻게 대응하나?</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>표준 명사 속성 대응표</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>Return, AfterSalesServiceRequest, CorrectiveActionRequest</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>QM01, QM04</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>반품(Return)·사후서비스신청에 일부 대응, 클레임 유형·회신 기한·금액은 Extension CustomerComplaint, Q-COST는 Extension QualityCost</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-01</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>8·9월 수요예측 정확도(전체·고객별)는?</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>(1 − Σ|실수주 − 예측| / Σ 실수주) × 100</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>SalesPlan, SalesOrderLine</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>SC01</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>8월 94.45%, 9월 94.51%. C001 96.05/96.47, C002 92.10/91.89, C003 79.17/75.00%</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-02</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>판단</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>수요예측 정확도가 가장 낮은 고객과 원인은?</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>고객별 정확도·수주 패턴</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>SalesPlan, SalesOrderHeader, CustomerPartyMaster</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>SC01</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>C003(보수용 AM) 75~79% — 주 1회 소량·수량 변동</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-03</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>10월(1~20일) 판매계획준수율은?</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>Σ 출하 / (계획 × 경과 영업일/월 영업일)</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>SalesPlan, ProductRelease</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>SC02</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>94.05%(C001 93.82, C002 95.75, C003 77.14%)</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-04</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>월별 생산계획준수율은?</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>Σ min(일 입고, 일 계획) / Σ 일 계획</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>ProductionPlanning, ProductIncoming</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>SC03</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>8월 93.10%, 9월 94.51%, 10월 89.11%</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-05</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>10월 자재충족율과 결품 제조오더는?</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>착수 점검에서 결품 없는 오더 / 점검 오더</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>AvailableInventory, ProductionOrder</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>SC04</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>94.12%(32/34). MO261006002 PCB-EWP24 24EA, MO261012002 MTR-24V 40EA 부족</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-06</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>MO261012002 자재 결품의 원인은?</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>결품 자품목 → 구매발주·입고</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>AvailableInventory, PurchaseOrderLine, GoodsReceipt</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>SC04</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>MTR-24V(V002 세진모터) 10-12 분할 납품 — 오전 60EA만 입고, 잔량 오후</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-07</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>10월 재고 보유일수(제품·자재·전체)는?</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>월말 재고금액 / 일평균 출고금액</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>Inventory, GoodsIssue</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>SC06</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>제품 1.69일, 자재·반제품 5.65일, 전체 3.59일</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-08</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>10월 재고회전율(연환산)은?</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>연환산 출고금액 / 평균 재고금액</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>Inventory, GoodsIssue</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>SC07</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>전체 117.4회(제품 168.7, 자재·반제품 88.3)</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-09</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>9월 재고실사 정확도와 차이 품목은?</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>장부 = 실사 품목 비율, 수량 정확도</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>InventoryCount</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>SC08</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>품목 85.71%(18/21), 수량 98.92%. ORG-45 −120, BLT-M5X16 −300, EWP-B200 −4</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-10</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>실사 차이는 언제 어떻게 장부에 반영됐나?</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>실사 후 조정 출고</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>InventoryCount, GoodsIssue</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>SC08</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>10-01 조정 출고(ADJ, 비고 '9월 실사 차이 조정') 3건</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-11</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>10-20 기준 장기 체화 재고 비율과 대상은?</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>입고 후 180일 초과 재고금액 / 총 재고금액</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>Inventory, Lot, GoodsReceipt</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>SC09</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>6.31%(12,060,000원): EWP-A090 150EA, HSG-A090 300EA(2024-02 입고), PCB-EWP12 격리 LOT V003-250920Q 300EA</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-12</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>판단</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>장기 체화 재고 처리 우선순위는?</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>금액 기준</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>Inventory, ItemMaster</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>SC09</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>EWP-A090 7,350,000원(61%) → HSG-A090 2,760,000원 → PCB-EWP12 1,950,000원</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-13</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>10월 납기이행율과 지연 수주는?</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>요청일까지 전량 출하된 라인 / 요청일 도래 라인</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>SalesOrderLine, ProductRelease, DeliveryLine</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>CS01</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>82.35%(28/34). C001 68.75% — SO260926001·0928001·0929001·0930001·1001001 각 1~2일 지연, C003 SO261007003 1일 지연</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-14</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>10월 제품 품절율과 품절일은?</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>영업일 마감 재고 0 이하 비율</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>CS02</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>EWP-A100 37.5%(6/16일: 10-06~10-10, 10-12), EWP-B200 0%</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-15</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>10월 결품율은?</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>Σ 요청일 미출하 수량 / Σ 요청 수량</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>SalesOrderLine, DeliveryLine</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>CS03</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>5.70%(496/8,705EA). C001 8.12%, C003 16.47%, C002 0%</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-16</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>10월 6~12일 A100 품절·납기 지연의 근본 원인은?</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>품절 → 생산입고 감소 → 보류 LOT → 품질 원인</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>Inventory, ProductIncoming, Lot, ProductionPerformanceQuality</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>CS02, CS01, SC03</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>보류 LOT 4개(누설, EV2)로 10-03~07 포장 양품 절반 → 제품 재고 소진 → OE 우선 출하로 C003까지 지연</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-17</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>판단</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>보류 LOT E261003A1을 특채 출하한 결정의 결과는?</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>특채 출하 이후 클레임·비용</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>Lot, ProductRelease, Return</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>CS01, QM03, QM04</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>10-08 C001 출하로 납기 1건은 맞췄으나 10-12 라인 중단(15,000,000원)·10-13 누수 9EA 클레임 발생 → 10월 Q-COST 6.24%</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-18</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>조회</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>MES 도입 전(8월) 생산 실적은 어디에서 확인하나?</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>ERP 생산입고 이력</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>ProductIncoming</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>PR01</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>ERP 생산입고(src=HIST) — A100 9,670EA, B200 4,854EA</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-19</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>집계</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>월 매출액(출하 × 판매단가)은?</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>출하일 기준</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>ProductRelease, SalesOrderLine</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>QM04</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>8월 1,125,860,000원, 9월 1,127,360,000원, 10월(1~20일) 713,346,000원</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Q-SC07-20</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>진단</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>PSI KPI 산출에 필요하지만 KS X 9101 Core에 없는 속성은?</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>KPI 산식 속성 vs 표준 속성</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>SalesPlan, SalesOrderLine, Inventory, AvailableInventory</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>SC01, SC06, SC09, SC04, QM04</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>SalesPlan 계획유형·고객·버전, SalesOrderLine 판매단가, Inventory 기준일·LOT·입고일, AvailableInventory 제조오더·점검일, 표준원가(StandardCost)</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I101"/>
+  <autoFilter ref="A1:J156"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4815,7 +7635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4827,6 +7647,7 @@
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4875,6 +7696,11 @@
           <t>기대 답 보유</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>KPI 연결</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -4906,6 +7732,9 @@
       <c r="I2" s="2" t="n">
         <v>12</v>
       </c>
+      <c r="J2" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4914,16 +7743,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>3</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>1</v>
@@ -4932,10 +7761,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -4968,6 +7800,9 @@
       <c r="I4" s="2" t="n">
         <v>8</v>
       </c>
+      <c r="J4" s="2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4979,13 +7814,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0</v>
@@ -4994,10 +7829,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -5010,10 +7848,10 @@
         <v>2</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>6</v>
@@ -5025,14 +7863,85 @@
         <v>1</v>
       </c>
       <c r="H6" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SC06 고객·협력사 품질</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>10</v>
+      <c r="I7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SC07 PSI·고객서비스</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I6"/>
+  <autoFilter ref="A1:J8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5043,18 +7952,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>명사</t>
+          <t>KPI ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -5064,372 +7973,522 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>시나리오</t>
+          <t>질의 ID</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Lot</t>
+          <t>CS01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>SC02, SC03, SC04, SC05</t>
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC07-13, Q-SC07-16, Q-SC07-17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TraceParameter</t>
+          <t>CS02</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>SC03, SC04, SC05</t>
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC07-14, Q-SC07-16</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ProductionPerformanceQuality</t>
+          <t>CS03</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>SC02, SC03, SC04, SC05</t>
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC07-15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>OperationStart</t>
+          <t>EQ01</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>SC01, SC02, SC03, SC04, SC05</t>
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>EquipmentState</t>
+          <t>EQ02</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>SC04</t>
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC04-21</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>OperationEnd</t>
+          <t>EQ03</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>SC02, SC03, SC04</t>
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC04-25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>EQ04</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>SC01, SC02, SC03, SC04, SC05</t>
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC04-22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ItemMaster</t>
+          <t>EQ05</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>SC01, SC05</t>
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC04-22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ProductionOrder</t>
+          <t>EQ06</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>SC02, SC05</t>
+        <v>2</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC04-21, Q-SC04-22</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Alarm</t>
+          <t>EQ07</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>SC03, SC04, SC05</t>
+        <v>2</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC04-21, Q-SC04-23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>EquipmentParameter</t>
+          <t>EQ08</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>SC03</t>
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC04-21</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>PR01</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>SC01, SC02, SC04</t>
+        <v>2</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC02-21, Q-SC07-18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>BOMLine</t>
+          <t>PR02</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>SC01</t>
+        <v>3</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC02-22, Q-SC02-23, Q-SC06-03</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CommonCodeMaster</t>
+          <t>PR03</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>SC01, SC03, SC04, SC05</t>
+        <v>1</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC05-22</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Personnel</t>
+          <t>PR04</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>SC01, SC02, SC05</t>
+        <v>2</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC05-23, Q-SC05-25</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RoutingLine</t>
+          <t>PR05</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>SC01, SC02, SC03</t>
+        <v>2</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC06-09, Q-SC06-10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ProductionPerformance</t>
+          <t>QM01</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>SC02, SC05</t>
+        <v>4</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC06-01, Q-SC06-06, Q-SC06-17, Q-SC06-20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>BOMHeader</t>
+          <t>QM02</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>SC01</t>
+        <v>1</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC06-04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>UOMGroupLine</t>
+          <t>QM03</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>SC01, SC03</t>
+        <v>5</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC02-23, Q-SC06-02, Q-SC06-03, Q-SC06-05, Q-SC07-17</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RoutingHeader</t>
+          <t>QM04</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>SC01</t>
+        <v>7</v>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC06-07, Q-SC06-08, Q-SC06-09, Q-SC06-20, Q-SC07-17, Q-SC07-19, Q-SC07-20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Plant</t>
+          <t>QM05</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>SC01</t>
+        <v>1</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC05-21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>QM06</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>SC01, SC02</t>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC05-24, Q-SC05-25</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>QM07</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>SC01</t>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC06-11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>OperationEquipment</t>
+          <t>QM08</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC06-12, Q-SC06-13, Q-SC06-17, Q-SC06-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>QM09</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC06-14, Q-SC06-15, Q-SC06-16, Q-SC06-18, Q-SC06-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SC01</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC07-01, Q-SC07-02, Q-SC07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SC02</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>SC01</t>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>SC03</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC02-24, Q-SC07-04, Q-SC07-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SC04</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC06-16, Q-SC07-05, Q-SC07-06, Q-SC07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>SC05</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC02-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>SC06</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC07-07, Q-SC07-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>SC07</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>SC08</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC07-09, Q-SC07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>SC09</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Q-SC07-11, Q-SC07-12, Q-SC07-20</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C25"/>
+  <autoFilter ref="A1:C35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5440,7 +8499,704 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:C45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>명사</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>질의 수</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>시나리오</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>SC02, SC03, SC04, SC05, SC06, SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>ProductionPerformanceQuality</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>SC02, SC03, SC04, SC05, SC06, SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TraceParameter</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>SC03, SC04, SC05</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>OperationStart</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>SC01, SC02, SC03, SC04, SC05, SC06</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>EquipmentState</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>SC04</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>OperationEnd</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>SC02, SC03, SC04, SC05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ItemMaster</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>SC01, SC05, SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>SC01, SC02, SC03, SC04, SC05</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ProductionOrder</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>SC02, SC05, SC06, SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Return</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>SC06, SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ProductRelease</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>SC02, SC06, SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Alarm</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>SC03, SC04, SC05</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>EquipmentParameter</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>SC03</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>RoutingLine</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>SC01, SC02, SC03, SC04</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>CorrectiveActionRequest</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>SC06</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>SC01, SC02, SC04</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SalesOrderLine</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>SC06, SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SupplierInspectionResult</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>SC06</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>CommonCodeMaster</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>SC01, SC03, SC04, SC05</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ProductIncoming</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>SC02, SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>BOMLine</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>SC01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>AvailableInventory</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>SC06, SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Personnel</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>SC01, SC02, SC05</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ProductionPerformance</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>SC02, SC05</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SalesPlan</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>GoodsReceipt</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>SC06, SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>GoodsIssue</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>SC05, SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>BOMHeader</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>SC01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>AfterSalesServiceRequest</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>SC06</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>UOMGroupLine</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>SC01, SC03</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>RoutingHeader</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>SC01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>InventoryCount</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>CorrectiveActionResult</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>SC06</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Plant</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>SC01</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>SC01, SC02</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ProductionPlanning</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>SC02, SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>VendorPartyMaster</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>SC06</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>DeliveryLine</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>CustomerPartyMaster</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>SC06, SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>PurchaseOrderLine</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Department</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>SC01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>SalesOrderHeader</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>SC07</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>OperationEquipment</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>SC01</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C45"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5603,8 +9359,118 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>EV7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>보류 LOT 특채 출하 → 고객 라인 중단</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08 ~ 10-13</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>MES 보류(H) LOT E261003A1 179EA를 ERP에서 수기 특채 입고(PR261008SP1, src=MAN) → 10-08 C001 출하(SO260928001) → 10-12 고객 라인 40분 중단 클레임 CL2610-001(1,500만원), 10-13 선별 누수 9EA(CL2610-002, 회신 기한 10-19 미회신)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>EV8</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>제품 A100 품절·납기 지연</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06 ~ 10-12</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>보류 LOT 4개로 10-03·05·06·07 포장 양품이 절반(193~195EA) → 제품 재고 소진(품절 6일) → 납기 지연 6라인(C001 5, C003 1), 결품 496EA. OE(C001) 우선 출하로 AM(C003)이 더 늦음</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>EV9</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>자재 결품</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05 ~ 10-12</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>10-05 PCB-EWP24 수입검사 불합격(V003 납땜 불량 5EA) → 10-06 오후 대체 납품 → MO261006002 착수 점검 24EA 부족. 10-12 MTR-24V(V002) 분할 납품(오전 60EA) → MO261012002 40EA 부족</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>EV10</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>협력업체 V003 커넥터 연쇄 부적합</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21 ~ 10-05</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>9-21 CON-3P 수입검사 특채(S, 외관 2EA) → 9-27 라인 발견 6EA → 9-29 C002 커넥터 접촉불량 클레임(CL2609-003)·고객 발견 NCR2609902(CAR 미완료). 10-05 PCB-EWP24 불합격까지 V003 부적합 4건</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>EV11</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>재고 실사 차이·장기 체화</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30 실사, 10-20 기준</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>실사 차이 3품목(ORG-45 −120, BLT-M5X16 −300, EWP-B200 −4) → 10-01 조정 출고(ADJ). 장기 체화: PCB-EWP12 격리 LOT V003-250920Q 300EA, 단종 EWP-A090 150EA·HSG-A090 300EA(2024-02 입고) = 1,206만원(6.31%)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D7"/>
+  <autoFilter ref="A1:D12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/mapping/impix/s1/S1_업무질의서_IMPIX.xlsx
+++ b/mapping/impix/s1/S1_업무질의서_IMPIX.xlsx
@@ -8557,7 +8557,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TraceParameter</t>
+          <t>OperationStart</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -8565,14 +8565,14 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SC03, SC04, SC05</t>
+          <t>SC01, SC02, SC03, SC04, SC05, SC06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>OperationStart</t>
+          <t>TraceParameter</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SC01, SC02, SC03, SC04, SC05, SC06</t>
+          <t>SC03, SC04, SC05</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>EquipmentParameter</t>
+          <t>RoutingLine</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -8730,14 +8730,14 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>SC03</t>
+          <t>SC01, SC02, SC03, SC04</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RoutingLine</t>
+          <t>EquipmentParameter</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -8745,14 +8745,14 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>SC01, SC02, SC03, SC04</t>
+          <t>SC03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CorrectiveActionRequest</t>
+          <t>SupplierInspectionResult</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -8767,7 +8767,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>SalesOrderLine</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -8775,14 +8775,14 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SC01, SC02, SC04</t>
+          <t>SC06, SC07</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>SalesOrderLine</t>
+          <t>Operation</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -8790,14 +8790,14 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SC06, SC07</t>
+          <t>SC01, SC02, SC04</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>SupplierInspectionResult</t>
+          <t>CorrectiveActionRequest</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -8812,7 +8812,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CommonCodeMaster</t>
+          <t>BOMLine</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SC01, SC03, SC04, SC05</t>
+          <t>SC01</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8842,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>BOMLine</t>
+          <t>CommonCodeMaster</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>SC01</t>
+          <t>SC01, SC03, SC04, SC05</t>
         </is>
       </c>
     </row>
@@ -8872,7 +8872,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Personnel</t>
+          <t>GoodsIssue</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -8880,14 +8880,14 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SC01, SC02, SC05</t>
+          <t>SC05, SC07</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ProductionPerformance</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -8895,14 +8895,14 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>SC02, SC05</t>
+          <t>SC06, SC07</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SalesPlan</t>
+          <t>ProductionPerformance</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -8910,14 +8910,14 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>SC07</t>
+          <t>SC02, SC05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>Personnel</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -8925,14 +8925,14 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>SC06, SC07</t>
+          <t>SC01, SC02, SC05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>GoodsIssue</t>
+          <t>SalesPlan</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
@@ -8940,14 +8940,14 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>SC05, SC07</t>
+          <t>SC07</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BOMHeader</t>
+          <t>AfterSalesServiceRequest</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
@@ -8955,14 +8955,14 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>SC01</t>
+          <t>SC06</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>AfterSalesServiceRequest</t>
+          <t>BOMHeader</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
@@ -8970,14 +8970,14 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>SC06</t>
+          <t>SC01</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>UOMGroupLine</t>
+          <t>InventoryCount</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -8985,14 +8985,14 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>SC01, SC03</t>
+          <t>SC07</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>RoutingHeader</t>
+          <t>CorrectiveActionResult</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -9000,14 +9000,14 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>SC01</t>
+          <t>SC06</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>InventoryCount</t>
+          <t>VendorPartyMaster</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -9015,14 +9015,14 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>SC07</t>
+          <t>SC06</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>CorrectiveActionResult</t>
+          <t>RoutingHeader</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -9030,14 +9030,14 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>SC06</t>
+          <t>SC01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Plant</t>
+          <t>UOMGroupLine</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -9045,14 +9045,14 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>SC01</t>
+          <t>SC01, SC03</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>CustomerPartyMaster</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -9060,7 +9060,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>SC01, SC02</t>
+          <t>SC06, SC07</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9082,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>VendorPartyMaster</t>
+          <t>Plant</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>SC06</t>
+          <t>SC01</t>
         </is>
       </c>
     </row>
@@ -9112,7 +9112,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>CustomerPartyMaster</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -9120,14 +9120,14 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>SC06, SC07</t>
+          <t>SC01, SC02</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>PurchaseOrderLine</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -9135,14 +9135,14 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>SC07</t>
+          <t>SC01</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>OperationEquipment</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -9157,7 +9157,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SalesOrderHeader</t>
+          <t>PurchaseOrderLine</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -9172,7 +9172,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>OperationEquipment</t>
+          <t>SalesOrderHeader</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>SC01</t>
+          <t>SC07</t>
         </is>
       </c>
     </row>

--- a/mapping/impix/s1/S1_업무질의서_IMPIX.xlsx
+++ b/mapping/impix/s1/S1_업무질의서_IMPIX.xlsx
@@ -8557,7 +8557,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>OperationStart</t>
+          <t>TraceParameter</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -8565,14 +8565,14 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SC01, SC02, SC03, SC04, SC05, SC06</t>
+          <t>SC03, SC04, SC05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TraceParameter</t>
+          <t>OperationStart</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>SC03, SC04, SC05</t>
+          <t>SC01, SC02, SC03, SC04, SC05, SC06</t>
         </is>
       </c>
     </row>
@@ -8647,7 +8647,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ProductionOrder</t>
+          <t>Return</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
@@ -8655,14 +8655,14 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>SC02, SC05, SC06, SC07</t>
+          <t>SC06, SC07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>ProductionOrder</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>SC06, SC07</t>
+          <t>SC02, SC05, SC06, SC07</t>
         </is>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>RoutingLine</t>
+          <t>EquipmentParameter</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -8730,14 +8730,14 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>SC01, SC02, SC03, SC04</t>
+          <t>SC03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>EquipmentParameter</t>
+          <t>RoutingLine</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -8745,14 +8745,14 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>SC03</t>
+          <t>SC01, SC02, SC03, SC04</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SupplierInspectionResult</t>
+          <t>CorrectiveActionRequest</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -8767,7 +8767,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SalesOrderLine</t>
+          <t>Operation</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
@@ -8775,14 +8775,14 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>SC06, SC07</t>
+          <t>SC01, SC02, SC04</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>SupplierInspectionResult</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
@@ -8790,14 +8790,14 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>SC01, SC02, SC04</t>
+          <t>SC06</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CorrectiveActionRequest</t>
+          <t>SalesOrderLine</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -8805,14 +8805,14 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>SC06</t>
+          <t>SC06, SC07</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>BOMLine</t>
+          <t>CommonCodeMaster</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -8820,14 +8820,14 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>SC01</t>
+          <t>SC01, SC03, SC04, SC05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ProductIncoming</t>
+          <t>BOMLine</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
@@ -8835,14 +8835,14 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>SC02, SC07</t>
+          <t>SC01</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CommonCodeMaster</t>
+          <t>ProductIncoming</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
@@ -8850,14 +8850,14 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>SC01, SC03, SC04, SC05</t>
+          <t>SC02, SC07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AvailableInventory</t>
+          <t>Personnel</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
@@ -8865,14 +8865,14 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>SC06, SC07</t>
+          <t>SC01, SC02, SC05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GoodsIssue</t>
+          <t>GoodsReceipt</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
@@ -8880,14 +8880,14 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>SC05, SC07</t>
+          <t>SC06, SC07</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GoodsReceipt</t>
+          <t>AvailableInventory</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
@@ -8902,7 +8902,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ProductionPerformance</t>
+          <t>GoodsIssue</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
@@ -8910,14 +8910,14 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>SC02, SC05</t>
+          <t>SC05, SC07</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Personnel</t>
+          <t>ProductionPerformance</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>SC01, SC02, SC05</t>
+          <t>SC02, SC05</t>
         </is>
       </c>
     </row>
@@ -8977,7 +8977,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>InventoryCount</t>
+          <t>CustomerPartyMaster</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
@@ -8985,14 +8985,14 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>SC07</t>
+          <t>SC06, SC07</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>CorrectiveActionResult</t>
+          <t>Plant</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
@@ -9000,14 +9000,14 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>SC06</t>
+          <t>SC01</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>VendorPartyMaster</t>
+          <t>InventoryCount</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
@@ -9015,14 +9015,14 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>SC06</t>
+          <t>SC07</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RoutingHeader</t>
+          <t>UOMGroupLine</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
@@ -9030,14 +9030,14 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>SC01</t>
+          <t>SC01, SC03</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>UOMGroupLine</t>
+          <t>RoutingHeader</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
@@ -9045,14 +9045,14 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>SC01, SC03</t>
+          <t>SC01</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>CustomerPartyMaster</t>
+          <t>DeliveryLine</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
@@ -9060,14 +9060,14 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>SC06, SC07</t>
+          <t>SC07</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ProductionPlanning</t>
+          <t>VendorPartyMaster</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
@@ -9075,14 +9075,14 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>SC02, SC07</t>
+          <t>SC06</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Plant</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
@@ -9090,14 +9090,14 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>SC01</t>
+          <t>SC01, SC02</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>DeliveryLine</t>
+          <t>CorrectiveActionResult</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
@@ -9105,14 +9105,14 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>SC07</t>
+          <t>SC06</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Line</t>
+          <t>ProductionPlanning</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
@@ -9120,14 +9120,14 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>SC01, SC02</t>
+          <t>SC02, SC07</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>PurchaseOrderLine</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
@@ -9135,14 +9135,14 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>SC01</t>
+          <t>SC07</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>OperationEquipment</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
@@ -9157,7 +9157,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>PurchaseOrderLine</t>
+          <t>OperationEquipment</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>SC07</t>
+          <t>SC01</t>
         </is>
       </c>
     </row>
